--- a/output/pdf_financials_xlsx/DGTL.H.xlsx
+++ b/output/pdf_financials_xlsx/DGTL.H.xlsx
@@ -2751,22 +2751,22 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.233044</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.311338</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.347859</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.414192</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.451686</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.484157</v>
       </c>
     </row>
     <row r="93">
@@ -4790,7 +4790,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -5766,7 +5770,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -6468,7 +6476,11 @@
           <t>Reserves (Note 12)</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -7058,7 +7070,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -7766,7 +7782,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E86" s="5" t="n">
         <v>0.233044</v>
       </c>

--- a/output/pdf_financials_xlsx/DGTL.H.xlsx
+++ b/output/pdf_financials_xlsx/DGTL.H.xlsx
@@ -653,22 +653,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.475034</v>
+        <v>1.264247</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2.317663</v>
+        <v>6.006317</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.417263</v>
+        <v>3.907993</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1.047122</v>
+        <v>2.467542</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.470979</v>
+        <v>0.722584</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.411556</v>
+        <v>0.5334950000000001</v>
       </c>
     </row>
     <row r="11">
@@ -712,13 +712,13 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000161</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>1.7e-05</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.00262</v>
       </c>
     </row>
     <row r="13">
@@ -1129,13 +1129,13 @@
         <v>-4.928862</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.543921</v>
+        <v>-2.544082</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.9852109999999999</v>
+        <v>-0.985228</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.151217</v>
+        <v>0.148597</v>
       </c>
     </row>
     <row r="28">
@@ -1179,13 +1179,13 @@
         <v>-4.170177</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.375646</v>
+        <v>-2.375807</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.9852109999999999</v>
+        <v>-0.985228</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.151217</v>
+        <v>0.148597</v>
       </c>
     </row>
     <row r="30">
@@ -1204,7 +1204,7 @@
         <v>-165.7888051587152</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-98.56221276927654</v>
+        <v>-98.56889243293679</v>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
@@ -1285,22 +1285,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.958162</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.111448</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.411219</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.405786</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.103596</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.215051</v>
       </c>
     </row>
     <row r="35">
@@ -1335,22 +1335,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.958162</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.111448</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.411219</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.405786</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.103596</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.215051</v>
       </c>
     </row>
     <row r="37">
@@ -1635,19 +1635,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.473828</v>
+        <v>0.515666</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.857291</v>
+        <v>0.745843</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.801639</v>
+        <v>0.39042</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.624185</v>
+        <v>0.218399</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.105103</v>
+        <v>0.001507</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0</v>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E175" s="5" t="n">
@@ -11932,26 +11932,26 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E179" s="5" t="n">
-        <v>-1.264247</v>
+        <v>1.264247</v>
       </c>
       <c r="F179" s="5" t="n">
-        <v>-6.006317</v>
+        <v>6.006317</v>
       </c>
       <c r="G179" s="5" t="n">
-        <v>-3.907993</v>
+        <v>3.907993</v>
       </c>
       <c r="H179" s="5" t="n">
-        <v>-2.467542</v>
+        <v>2.467542</v>
       </c>
       <c r="I179" s="5" t="n">
-        <v>-0.722584</v>
+        <v>0.722584</v>
       </c>
       <c r="J179" s="5" t="n">
-        <v>-0.5334950000000001</v>
+        <v>0.5334950000000001</v>
       </c>
     </row>
     <row r="180">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">

--- a/output/pdf_financials_xlsx/DGTL.H.xlsx
+++ b/output/pdf_financials_xlsx/DGTL.H.xlsx
@@ -936,13 +936,13 @@
         <v>-4.490862</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.024272</v>
+        <v>-2.543921</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-0.579358</v>
+        <v>-0.405853</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.487628</v>
+        <v>-0.336411</v>
       </c>
     </row>
     <row r="21">
@@ -961,13 +961,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0</v>
+        <v>0.024272</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
+        <v>-0.579358</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0</v>
+        <v>0.487628</v>
       </c>
     </row>
     <row r="22">
@@ -2129,19 +2129,19 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.938696</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.790445</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.104274</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.096774</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.06973600000000001</v>
       </c>
     </row>
     <row r="68">
@@ -9688,7 +9688,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E129" s="5" t="n">
         <v>-0.273</v>
       </c>
@@ -10314,7 +10318,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -12234,7 +12242,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -12276,7 +12288,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>NetIncomeDiscontinuousOperations</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -14756,7 +14768,11 @@
           <t>Net income from discontinued operations (Note 5)</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
